--- a/Outputs/Scenarios/PtX_demand_AT_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_AT_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.00414387072335156</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001187980626378903</v>
+        <v>0.0001385977397442053</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3.959935421263009e-05</v>
+        <v>4.15793219232616e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1370,7 +1370,7 @@
         <v>0.002010144934382977</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0007784721901564351</v>
+        <v>0.0007784721901564352</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>5.970616272678076e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>3.959935421263009e-05</v>
+        <v>1.781970939568355e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006134496104582772</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0005947852721602929</v>
+        <v>0.0006939161508536751</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0001982617573867643</v>
+        <v>0.0002081748452561026</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0003228682160306722</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0001982617573867643</v>
+        <v>8.921779082404396e-05</v>
       </c>
     </row>
     <row r="43">
